--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -2453,10 +2453,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120851509</v>
+        <v>120851533</v>
       </c>
       <c r="B17" t="n">
-        <v>91127</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,25 +2465,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615604</v>
+        <v>615682</v>
       </c>
       <c r="R17" t="n">
-        <v>7004706</v>
+        <v>7004742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120851457</v>
+        <v>120851695</v>
       </c>
       <c r="B18" t="n">
-        <v>79708</v>
+        <v>82385</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,25 +2571,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615615</v>
+        <v>615647</v>
       </c>
       <c r="R18" t="n">
-        <v>7004779</v>
+        <v>7004750</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2668,7 @@
         <v>120851637</v>
       </c>
       <c r="B19" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120851695</v>
+        <v>120851610</v>
       </c>
       <c r="B20" t="n">
-        <v>82382</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,25 +2783,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615647</v>
+        <v>615553</v>
       </c>
       <c r="R20" t="n">
-        <v>7004750</v>
+        <v>7004688</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120851533</v>
+        <v>120851457</v>
       </c>
       <c r="B21" t="n">
-        <v>90973</v>
+        <v>79711</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,25 +2889,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615682</v>
+        <v>615615</v>
       </c>
       <c r="R21" t="n">
-        <v>7004742</v>
+        <v>7004779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,10 +2983,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120851610</v>
+        <v>120851509</v>
       </c>
       <c r="B22" t="n">
-        <v>98071</v>
+        <v>91137</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,21 +2999,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615553</v>
+        <v>615604</v>
       </c>
       <c r="R22" t="n">
-        <v>7004688</v>
+        <v>7004706</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -2453,10 +2453,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120851533</v>
+        <v>120851509</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>91137</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,25 +2465,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>615682</v>
+        <v>615604</v>
       </c>
       <c r="R17" t="n">
-        <v>7004742</v>
+        <v>7004706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120851695</v>
+        <v>120851457</v>
       </c>
       <c r="B18" t="n">
-        <v>82385</v>
+        <v>79711</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,25 +2571,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>615647</v>
+        <v>615615</v>
       </c>
       <c r="R18" t="n">
-        <v>7004750</v>
+        <v>7004779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120851637</v>
+        <v>120851610</v>
       </c>
       <c r="B19" t="n">
-        <v>90715</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2677,25 +2677,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>615626</v>
+        <v>615553</v>
       </c>
       <c r="R19" t="n">
-        <v>7004795</v>
+        <v>7004688</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2771,10 +2771,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120851610</v>
+        <v>120851637</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>90715</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,25 +2783,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>615553</v>
+        <v>615626</v>
       </c>
       <c r="R20" t="n">
-        <v>7004688</v>
+        <v>7004795</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120851457</v>
+        <v>120851533</v>
       </c>
       <c r="B21" t="n">
-        <v>79711</v>
+        <v>90983</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,25 +2889,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>615615</v>
+        <v>615682</v>
       </c>
       <c r="R21" t="n">
-        <v>7004779</v>
+        <v>7004742</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2983,10 +2983,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120851509</v>
+        <v>120851695</v>
       </c>
       <c r="B22" t="n">
-        <v>91137</v>
+        <v>82385</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,25 +2995,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>615604</v>
+        <v>615647</v>
       </c>
       <c r="R22" t="n">
-        <v>7004706</v>
+        <v>7004750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3086,6 +3086,210 @@
           <t>Sweco naturvärdesinventering och artinventering</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121538477</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57355</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Vemyra, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>615634</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7004668</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121538476</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90714</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vemyra, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>615681</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7004683</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Johanna Kühne</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -3194,7 +3194,7 @@
         <v>121538476</v>
       </c>
       <c r="B24" t="n">
-        <v>90714</v>
+        <v>90719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121538477</v>
+        <v>121538476</v>
       </c>
       <c r="B23" t="n">
-        <v>57355</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615634</v>
+        <v>615681</v>
       </c>
       <c r="R23" t="n">
-        <v>7004668</v>
+        <v>7004683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121538476</v>
+        <v>121538477</v>
       </c>
       <c r="B24" t="n">
-        <v>90719</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615681</v>
+        <v>615634</v>
       </c>
       <c r="R24" t="n">
-        <v>7004683</v>
+        <v>7004668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121538476</v>
+        <v>121538477</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615681</v>
+        <v>615634</v>
       </c>
       <c r="R23" t="n">
-        <v>7004683</v>
+        <v>7004668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121538477</v>
+        <v>121538476</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615634</v>
+        <v>615681</v>
       </c>
       <c r="R24" t="n">
-        <v>7004668</v>
+        <v>7004683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121538476</v>
+        <v>121538477</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615681</v>
+        <v>615634</v>
       </c>
       <c r="R23" t="n">
-        <v>7004683</v>
+        <v>7004668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121538477</v>
+        <v>121538476</v>
       </c>
       <c r="B24" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615634</v>
+        <v>615681</v>
       </c>
       <c r="R24" t="n">
-        <v>7004668</v>
+        <v>7004683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 52945-2019 artfynd.xlsx
+++ b/artfynd/A 52945-2019 artfynd.xlsx
@@ -3089,10 +3089,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121538477</v>
+        <v>121538476</v>
       </c>
       <c r="B23" t="n">
-        <v>57357</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>615634</v>
+        <v>615681</v>
       </c>
       <c r="R23" t="n">
-        <v>7004668</v>
+        <v>7004683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Klara Elmquist</t>
+          <t>Johanna Kühne</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121538476</v>
+        <v>121538477</v>
       </c>
       <c r="B24" t="n">
-        <v>90728</v>
+        <v>57357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>615681</v>
+        <v>615634</v>
       </c>
       <c r="R24" t="n">
-        <v>7004683</v>
+        <v>7004668</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johanna Kühne</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
